--- a/separarRelatorio/separarNeotin.xlsx
+++ b/separarRelatorio/separarNeotin.xlsx
@@ -15,441 +15,429 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="150">
   <si>
     <t>CISBAF x Marque fácil</t>
   </si>
   <si>
-    <t>Filtros aplicados: Modelo: Analitico | Visualização: MUNICIPIO | Agrupamento: Fornecedor | Situação: VALIDADO | Prestadores: 154 | Período: 20/03/2026 a 19/04/2026</t>
+    <t>Filtros aplicados: Modelo: Analitico | Visualização: MUNICIPIO | Agrupamento: Fornecedor | Situação: VALIDADO | Prestadores: 122 | Período: 20/03/2026 a 19/04/2026</t>
+  </si>
+  <si>
+    <t>MUNICIPIO: RJ - Mesquita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data / Hora </t>
+  </si>
+  <si>
+    <t>Paciente</t>
+  </si>
+  <si>
+    <t>Data de Nascimento</t>
+  </si>
+  <si>
+    <t>Procedimento</t>
+  </si>
+  <si>
+    <t>Quantidade</t>
+  </si>
+  <si>
+    <t>Valor Regional</t>
+  </si>
+  <si>
+    <t>Contraste</t>
+  </si>
+  <si>
+    <t>Sedação</t>
+  </si>
+  <si>
+    <t>Valor SUS</t>
+  </si>
+  <si>
+    <t>Valor Total</t>
+  </si>
+  <si>
+    <t>03/04/2026 08:00</t>
+  </si>
+  <si>
+    <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
+  </si>
+  <si>
+    <t>06/08/1977</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 14.879,62</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>R$ 1.384,38</t>
+  </si>
+  <si>
+    <t>R$ 16.264,00</t>
+  </si>
+  <si>
+    <t>20/03/2026 14:00</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+  </si>
+  <si>
+    <t>R$ 440,00</t>
+  </si>
+  <si>
+    <t>R$ 10,00</t>
+  </si>
+  <si>
+    <t>R$ 450,00</t>
+  </si>
+  <si>
+    <t>23/03/2026 09:00</t>
+  </si>
+  <si>
+    <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 390,00</t>
+  </si>
+  <si>
+    <t>R$ 400,00</t>
+  </si>
+  <si>
+    <t>SCHEILA SANTOS DA COSTA SILVA</t>
+  </si>
+  <si>
+    <t>18/02/1969</t>
+  </si>
+  <si>
+    <t>SERGIO RICARDO TRINDADE</t>
+  </si>
+  <si>
+    <t>30/09/1961</t>
+  </si>
+  <si>
+    <t>24/03/2026 14:00</t>
+  </si>
+  <si>
+    <t>ANA MARIA ARAUJO</t>
+  </si>
+  <si>
+    <t>18/01/1970</t>
+  </si>
+  <si>
+    <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>14/02/1984</t>
+  </si>
+  <si>
+    <t>30/03/2026 09:00</t>
+  </si>
+  <si>
+    <t>FABIANA DA SILVA TOSTA DA SILVA</t>
+  </si>
+  <si>
+    <t>15/03/1984</t>
+  </si>
+  <si>
+    <t>17/04/2026 08:00</t>
+  </si>
+  <si>
+    <t>R$ 7.439,81</t>
+  </si>
+  <si>
+    <t>R$ 692,19</t>
+  </si>
+  <si>
+    <t>R$ 8.132,00</t>
+  </si>
+  <si>
+    <t>ROSANGELA DE OLIVEIRA LIMA</t>
+  </si>
+  <si>
+    <t>16/10/1974</t>
+  </si>
+  <si>
+    <t>GLAUCIA DE OLIVEIRA MELLO</t>
+  </si>
+  <si>
+    <t>13/09/1988</t>
+  </si>
+  <si>
+    <t>LILIAN ALVES COELHO</t>
+  </si>
+  <si>
+    <t>27/01/1967</t>
+  </si>
+  <si>
+    <t>23/03/2026 08:00</t>
+  </si>
+  <si>
+    <t>EMANOEL ANTONIO BASILIO</t>
+  </si>
+  <si>
+    <t>01/11/1944</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
+  </si>
+  <si>
+    <t>05/04/2026 08:00</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE RESSECÇÃO ENDOSCÓPICA DE PRÓSTATA - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 13.648,42</t>
+  </si>
+  <si>
+    <t>R$ 851,58</t>
+  </si>
+  <si>
+    <t>R$ 14.500,00</t>
+  </si>
+  <si>
+    <t>20/03/2026 13:00</t>
+  </si>
+  <si>
+    <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
+  </si>
+  <si>
+    <t>20/11/1981</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - GINECOLOGIA</t>
+  </si>
+  <si>
+    <t>01/04/2026 13:00</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE HISTERECTOMIA TOTAL - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 9.782,56</t>
+  </si>
+  <si>
+    <t>R$ 1.103,64</t>
+  </si>
+  <si>
+    <t>R$ 10.886,20</t>
+  </si>
+  <si>
+    <t>31/03/2026 09:00</t>
+  </si>
+  <si>
+    <t>10/04/2026 08:00</t>
+  </si>
+  <si>
+    <t>Total do grupo:</t>
+  </si>
+  <si>
+    <t>R$ 136.718,32</t>
+  </si>
+  <si>
+    <t>R$ 11.865,88</t>
+  </si>
+  <si>
+    <t>R$ 148.584,20</t>
+  </si>
+  <si>
+    <t>MUNICIPIO: RJ - Queimados</t>
+  </si>
+  <si>
+    <t>27/03/2026 13:00</t>
+  </si>
+  <si>
+    <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
+  </si>
+  <si>
+    <t>02/10/2006</t>
+  </si>
+  <si>
+    <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+  </si>
+  <si>
+    <t>27/03/2026 09:00</t>
+  </si>
+  <si>
+    <t>DENILSON DA SILVA EVANGELISTA</t>
+  </si>
+  <si>
+    <t>06/02/1983</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE VASECTOMIA - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 5.411,13</t>
+  </si>
+  <si>
+    <t>R$ 438,87</t>
+  </si>
+  <si>
+    <t>R$ 5.850,00</t>
+  </si>
+  <si>
+    <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
+  </si>
+  <si>
+    <t>01/07/1982</t>
+  </si>
+  <si>
+    <t>04/04/2026 08:00</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 12.107,55</t>
+  </si>
+  <si>
+    <t>R$ 992,45</t>
+  </si>
+  <si>
+    <t>R$ 13.100,00</t>
+  </si>
+  <si>
+    <t>R$ 32.116,23</t>
+  </si>
+  <si>
+    <t>R$ 2.483,77</t>
+  </si>
+  <si>
+    <t>R$ 34.600,00</t>
+  </si>
+  <si>
+    <t>MUNICIPIO: RJ - Nova Iguaçu</t>
+  </si>
+  <si>
+    <t>SIMONE DA SILVA ARRUDA ARAUJO</t>
+  </si>
+  <si>
+    <t>07/09/1973</t>
+  </si>
+  <si>
+    <t>MARIA ROSELMA FERNANDES DA SILVA</t>
+  </si>
+  <si>
+    <t>27/09/1968</t>
+  </si>
+  <si>
+    <t>ROSIMERE VITORIA BARBOSA</t>
+  </si>
+  <si>
+    <t>02/03/1974</t>
+  </si>
+  <si>
+    <t>JOSELAINE ANCHIETA DA SILVA</t>
+  </si>
+  <si>
+    <t>12/10/1979</t>
+  </si>
+  <si>
+    <t>MARGARETE DA SILVA FARIAS</t>
+  </si>
+  <si>
+    <t>16/08/1955</t>
+  </si>
+  <si>
+    <t>AIRTON GERALDO CAMARGO</t>
+  </si>
+  <si>
+    <t>08/05/1959</t>
+  </si>
+  <si>
+    <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
+  </si>
+  <si>
+    <t>R$ 5.630,88</t>
+  </si>
+  <si>
+    <t>R$ 219,12</t>
+  </si>
+  <si>
+    <t>MARCOS VINICIUS LEMOS ACCIOLI</t>
+  </si>
+  <si>
+    <t>28/03/1980</t>
+  </si>
+  <si>
+    <t>JOSE MAXIMO PEREIRA</t>
+  </si>
+  <si>
+    <t>05/07/1943</t>
+  </si>
+  <si>
+    <t>11/04/2026 08:00</t>
+  </si>
+  <si>
+    <t>R$ 46.101,00</t>
+  </si>
+  <si>
+    <t>R$ 3.327,00</t>
+  </si>
+  <si>
+    <t>R$ 49.428,00</t>
+  </si>
+  <si>
+    <t>MUNICIPIO: RJ - Seropédica</t>
+  </si>
+  <si>
+    <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
+  </si>
+  <si>
+    <t>22/08/1973</t>
+  </si>
+  <si>
+    <t>SIMONE RAMOS DE ABREU</t>
+  </si>
+  <si>
+    <t>23/01/1970</t>
+  </si>
+  <si>
+    <t>ANTONIO SINHORINHO</t>
+  </si>
+  <si>
+    <t>13/06/1955</t>
+  </si>
+  <si>
+    <t>R$ 38.812,65</t>
+  </si>
+  <si>
+    <t>R$ 3.037,35</t>
+  </si>
+  <si>
+    <t>R$ 41.850,00</t>
   </si>
   <si>
     <t>MUNICIPIO: RJ - São João de Meriti</t>
   </si>
   <si>
-    <t xml:space="preserve">Data / Hora </t>
-  </si>
-  <si>
-    <t>Paciente</t>
-  </si>
-  <si>
-    <t>Data de Nascimento</t>
-  </si>
-  <si>
-    <t>Procedimento</t>
-  </si>
-  <si>
-    <t>Quantidade</t>
-  </si>
-  <si>
-    <t>Valor Regional</t>
-  </si>
-  <si>
-    <t>Contraste</t>
-  </si>
-  <si>
-    <t>Sedação</t>
-  </si>
-  <si>
-    <t>Valor SUS</t>
-  </si>
-  <si>
-    <t>Valor Total</t>
-  </si>
-  <si>
-    <t>02/04/2026 13:30</t>
-  </si>
-  <si>
-    <t>MARIA NEILA DE SOUSA BARROS</t>
-  </si>
-  <si>
-    <t>01/05/1978</t>
-  </si>
-  <si>
-    <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
-  </si>
-  <si>
-    <t>R$ 440,00</t>
-  </si>
-  <si>
-    <t>R$ 0,00</t>
-  </si>
-  <si>
-    <t>R$ 10,00</t>
-  </si>
-  <si>
-    <t>R$ 450,00</t>
-  </si>
-  <si>
-    <t>LIETE PEREIRA DE LIMA</t>
-  </si>
-  <si>
-    <t>29/03/1951</t>
-  </si>
-  <si>
-    <t>NORMA FONSECA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>05/07/1960</t>
-  </si>
-  <si>
-    <t>REGINA FATIMA SILVA FERREIRA</t>
-  </si>
-  <si>
-    <t>11/03/1962</t>
-  </si>
-  <si>
-    <t>14/04/2026 10:00</t>
-  </si>
-  <si>
-    <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 5.740,01</t>
-  </si>
-  <si>
-    <t>R$ 434,99</t>
-  </si>
-  <si>
-    <t>R$ 6.175,00</t>
-  </si>
-  <si>
-    <t>02/04/2026 07:00</t>
-  </si>
-  <si>
-    <t>PACOTE RISCO CIRURGICO - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 390,00</t>
-  </si>
-  <si>
-    <t>R$ 400,00</t>
-  </si>
-  <si>
-    <t>08/04/2026 07:00</t>
-  </si>
-  <si>
-    <t>JOSE ROBSON DA SILVA</t>
-  </si>
-  <si>
-    <t>16/07/1964</t>
-  </si>
-  <si>
-    <t>MARCELO RIBEIRO DA SILVA</t>
-  </si>
-  <si>
-    <t>05/05/1979</t>
-  </si>
-  <si>
-    <t>09/04/2026 07:00</t>
-  </si>
-  <si>
-    <t>CELIA DOS SANTOS PEDREIRO</t>
-  </si>
-  <si>
-    <t>31/12/1962</t>
-  </si>
-  <si>
-    <t>SUELI DO AMARAL RIBEIRO</t>
-  </si>
-  <si>
-    <t>24/04/1963</t>
-  </si>
-  <si>
-    <t>FRANCISCO DAS CHAGAS MORAIS</t>
-  </si>
-  <si>
-    <t>17/11/1963</t>
-  </si>
-  <si>
-    <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
-  </si>
-  <si>
-    <t>30/11/1963</t>
-  </si>
-  <si>
-    <t>01/04/2026 16:00</t>
-  </si>
-  <si>
-    <t>VALQUIRIA DOS SANTOS SILVA</t>
-  </si>
-  <si>
-    <t>19/11/1976</t>
-  </si>
-  <si>
-    <t>MARIA DE LOURDES DE SA VIANA</t>
-  </si>
-  <si>
-    <t>28/08/1965</t>
-  </si>
-  <si>
-    <t>08/04/2026 16:00</t>
-  </si>
-  <si>
-    <t>17/04/2026 08:00</t>
-  </si>
-  <si>
-    <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 5.635,08</t>
-  </si>
-  <si>
-    <t>R$ 539,92</t>
-  </si>
-  <si>
-    <t>10/04/2026 11:11</t>
-  </si>
-  <si>
-    <t>18/04/2026 08:00</t>
-  </si>
-  <si>
-    <t>Total do grupo:</t>
-  </si>
-  <si>
-    <t>R$ 54.110,22</t>
-  </si>
-  <si>
-    <t>R$ 3.889,78</t>
-  </si>
-  <si>
-    <t>R$ 58.000,00</t>
-  </si>
-  <si>
-    <t>MUNICIPIO: RJ - Queimados</t>
-  </si>
-  <si>
-    <t>02/04/2026 09:00</t>
-  </si>
-  <si>
-    <t>JOSIAS GOMES DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>26/12/1960</t>
-  </si>
-  <si>
-    <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
-  </si>
-  <si>
-    <t>10/04/2026 14:00</t>
-  </si>
-  <si>
-    <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 7.439,81</t>
-  </si>
-  <si>
-    <t>R$ 692,19</t>
-  </si>
-  <si>
-    <t>R$ 8.132,00</t>
-  </si>
-  <si>
-    <t>R$ 8.269,81</t>
-  </si>
-  <si>
-    <t>R$ 712,19</t>
-  </si>
-  <si>
-    <t>R$ 8.982,00</t>
-  </si>
-  <si>
-    <t>MUNICIPIO: RJ - Belford Roxo</t>
-  </si>
-  <si>
-    <t>NICE BATALHA RIBEIRO</t>
-  </si>
-  <si>
-    <t>12/12/1976</t>
-  </si>
-  <si>
-    <t>09/04/2026 09:00</t>
-  </si>
-  <si>
-    <t>RAYSSA SANTANA NASCIMENTO</t>
-  </si>
-  <si>
-    <t>05/08/2003</t>
-  </si>
-  <si>
-    <t>THIAGO PEREIRA CASSIANO</t>
-  </si>
-  <si>
-    <t>29/10/2001</t>
-  </si>
-  <si>
-    <t>SOLANGE AGOSTINHO</t>
-  </si>
-  <si>
-    <t>28/01/1959</t>
-  </si>
-  <si>
-    <t>17/04/2026 09:00</t>
-  </si>
-  <si>
-    <t>SARA LINO DA SILVA</t>
-  </si>
-  <si>
-    <t>28/11/1959</t>
-  </si>
-  <si>
-    <t>JOANA D ARC MOURA DA SILVA</t>
-  </si>
-  <si>
-    <t>23/06/1965</t>
-  </si>
-  <si>
-    <t>MANOEL DA SILVA ARRUDA</t>
-  </si>
-  <si>
-    <t>05/11/1957</t>
-  </si>
-  <si>
-    <t>15/04/2026 07:00</t>
-  </si>
-  <si>
-    <t>R$ 26.569,43</t>
-  </si>
-  <si>
-    <t>R$ 2.176,57</t>
-  </si>
-  <si>
-    <t>R$ 28.746,00</t>
-  </si>
-  <si>
-    <t>MUNICIPIO: RJ - Nilópolis</t>
-  </si>
-  <si>
-    <t>MILDNA BERNARDO REZENDE</t>
-  </si>
-  <si>
-    <t>21/11/1961</t>
-  </si>
-  <si>
-    <t>SUENIL DE OLIVEIRA GOMES</t>
-  </si>
-  <si>
-    <t>23/02/1952</t>
-  </si>
-  <si>
-    <t>RENATHA MENDES DA SILVA</t>
-  </si>
-  <si>
-    <t>08/12/1978</t>
-  </si>
-  <si>
-    <t>15/04/2026 16:00</t>
-  </si>
-  <si>
-    <t>JOSE HENRIQUE RODRIGUES</t>
-  </si>
-  <si>
-    <t>18/03/1955</t>
-  </si>
-  <si>
-    <t>CHRISTIANE PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>13/03/1974</t>
-  </si>
-  <si>
-    <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 5.212,03</t>
-  </si>
-  <si>
-    <t>R$ 637,97</t>
-  </si>
-  <si>
-    <t>R$ 5.850,00</t>
-  </si>
-  <si>
-    <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 12.107,55</t>
-  </si>
-  <si>
-    <t>R$ 992,45</t>
-  </si>
-  <si>
-    <t>R$ 13.100,00</t>
-  </si>
-  <si>
-    <t>R$ 31.641,62</t>
-  </si>
-  <si>
-    <t>R$ 2.783,38</t>
-  </si>
-  <si>
-    <t>R$ 34.425,00</t>
-  </si>
-  <si>
-    <t>MUNICIPIO: RJ - Nova Iguaçu</t>
-  </si>
-  <si>
-    <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
-  </si>
-  <si>
-    <t>22/09/1965</t>
-  </si>
-  <si>
-    <t>LEILA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>17/10/1956</t>
-  </si>
-  <si>
-    <t>CINTIA HONORATO SILVA</t>
-  </si>
-  <si>
-    <t>15/01/1977</t>
-  </si>
-  <si>
-    <t>11/04/2026 08:00</t>
-  </si>
-  <si>
-    <t>R$ 26.315,10</t>
-  </si>
-  <si>
-    <t>R$ 2.034,90</t>
-  </si>
-  <si>
-    <t>R$ 28.350,00</t>
-  </si>
-  <si>
-    <t>MUNICIPIO: RJ - Japeri</t>
-  </si>
-  <si>
-    <t>LIDIANE PINTO ROSA GOUDARD</t>
-  </si>
-  <si>
-    <t>05/05/1995</t>
-  </si>
-  <si>
-    <t>LEANDRO DA SILVA CONCEICAO</t>
-  </si>
-  <si>
-    <t>14/02/1980</t>
-  </si>
-  <si>
-    <t>CIRURGIA DE HERNIOPLASTIA EPIGASTRICA - ADULTO</t>
-  </si>
-  <si>
-    <t>R$ 5.048,27</t>
-  </si>
-  <si>
-    <t>R$ 801,73</t>
-  </si>
-  <si>
-    <t>R$ 24.555,83</t>
-  </si>
-  <si>
-    <t>R$ 2.269,17</t>
-  </si>
-  <si>
-    <t>R$ 26.825,00</t>
+    <t>ANA PAULA DE FIGUEIREDO SALES</t>
+  </si>
+  <si>
+    <t>07/03/1990</t>
+  </si>
+  <si>
+    <t>TADEU MARQUES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>10/07/1991</t>
+  </si>
+  <si>
+    <t>31/03/2026 14:00</t>
+  </si>
+  <si>
+    <t>R$ 17.073,44</t>
+  </si>
+  <si>
+    <t>R$ 1.362,76</t>
+  </si>
+  <si>
+    <t>R$ 18.436,20</t>
   </si>
   <si>
     <t>Quantidade total</t>
@@ -458,7 +446,7 @@
     <t>Total regional</t>
   </si>
   <si>
-    <t>R$ 171.462,01</t>
+    <t>R$ 270.821,64</t>
   </si>
   <si>
     <t>Total contraste</t>
@@ -470,13 +458,13 @@
     <t>Total valor SUS</t>
   </si>
   <si>
-    <t>R$ 13.865,99</t>
+    <t>R$ 22.076,76</t>
   </si>
   <si>
     <t>Total valor geral</t>
   </si>
   <si>
-    <t>R$ 185.328,00</t>
+    <t>R$ 292.898,40</t>
   </si>
 </sst>
 </file>
@@ -957,13 +945,13 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="37.419" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="41.133" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="50.559" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="67.127" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="65.984" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="18.71" bestFit="true" customWidth="true" style="0"/>
@@ -1042,7 +1030,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>17</v>
@@ -1062,22 +1050,22 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>16</v>
-      </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>18</v>
@@ -1086,30 +1074,30 @@
         <v>18</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E10" s="7">
         <v>1</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>18</v>
@@ -1118,30 +1106,30 @@
         <v>18</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="10" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>18</v>
@@ -1150,30 +1138,30 @@
         <v>18</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E12" s="7">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>18</v>
@@ -1182,62 +1170,62 @@
         <v>18</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="10">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="C14" s="7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E14" s="7">
         <v>1</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>18</v>
@@ -1246,62 +1234,62 @@
         <v>18</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="10" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="D16" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E16" s="7">
         <v>1</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>18</v>
@@ -1310,30 +1298,30 @@
         <v>18</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="10" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E17" s="10">
         <v>1</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>18</v>
@@ -1342,30 +1330,30 @@
         <v>18</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E18" s="7">
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>18</v>
@@ -1374,30 +1362,30 @@
         <v>18</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="D19" s="11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E19" s="10">
         <v>1</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>18</v>
@@ -1406,30 +1394,30 @@
         <v>18</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="D20" s="8" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E20" s="7">
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>18</v>
@@ -1438,30 +1426,30 @@
         <v>18</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="D21" s="11" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E21" s="10">
         <v>1</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>18</v>
@@ -1470,30 +1458,30 @@
         <v>18</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="7" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E22" s="7">
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>18</v>
@@ -1502,30 +1490,30 @@
         <v>18</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="10" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E23" s="10">
         <v>1</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>18</v>
@@ -1534,21 +1522,21 @@
         <v>18</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>16</v>
@@ -1557,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>18</v>
@@ -1566,30 +1554,30 @@
         <v>18</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="10" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E25" s="10">
         <v>1</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>18</v>
@@ -1598,15 +1586,15 @@
         <v>18</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>48</v>
@@ -1615,13 +1603,13 @@
         <v>49</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E26" s="7">
         <v>1</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>18</v>
@@ -1630,27 +1618,27 @@
         <v>18</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="10" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>17</v>
@@ -1670,22 +1658,22 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E28" s="7">
         <v>1</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>18</v>
@@ -1694,30 +1682,30 @@
         <v>18</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="10" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E29" s="10">
         <v>1</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>18</v>
@@ -1726,30 +1714,30 @@
         <v>18</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="E30" s="7">
         <v>1</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>18</v>
@@ -1758,30 +1746,30 @@
         <v>18</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="10" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E31" s="10">
         <v>1</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>18</v>
@@ -1790,10 +1778,10 @@
         <v>18</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1801,19 +1789,19 @@
         <v>56</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E32" s="7">
         <v>1</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>18</v>
@@ -1822,30 +1810,30 @@
         <v>18</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="E33" s="10">
         <v>1</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>18</v>
@@ -1854,30 +1842,30 @@
         <v>18</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E34" s="7">
         <v>1</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>18</v>
@@ -1886,296 +1874,323 @@
         <v>18</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="10" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B35" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D37" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="10">
+        <v>2</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="10">
+        <v>2</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="14">
+        <v>38</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1</v>
+      </c>
+      <c r="F44" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="10">
-        <v>1</v>
-      </c>
-      <c r="F35" s="12" t="s">
+      <c r="G44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="14">
-        <v>28</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="10">
-        <v>1</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="14">
-        <v>3</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E45" s="7">
         <v>1</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>18</v>
@@ -2184,30 +2199,30 @@
         <v>18</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E46" s="10">
         <v>1</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>18</v>
@@ -2216,30 +2231,30 @@
         <v>18</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="E47" s="7">
         <v>1</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>18</v>
@@ -2248,30 +2263,30 @@
         <v>18</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B48" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="C48" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E48" s="10">
         <v>1</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>18</v>
@@ -2280,30 +2295,30 @@
         <v>18</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="E49" s="7">
         <v>1</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>18</v>
@@ -2312,30 +2327,30 @@
         <v>18</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E50" s="10">
         <v>1</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>18</v>
@@ -2344,30 +2359,30 @@
         <v>18</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="E51" s="7">
         <v>1</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>18</v>
@@ -2376,126 +2391,99 @@
         <v>18</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E52" s="10">
-        <v>1</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>20</v>
+      <c r="A52" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="14">
+        <v>9</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" s="7">
-        <v>1</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="A53" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="10">
-        <v>1</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G54" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>75</v>
+      <c r="A54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E55" s="7">
         <v>1</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>18</v>
@@ -2504,30 +2492,30 @@
         <v>18</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="10" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E56" s="10">
         <v>1</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>18</v>
@@ -2536,30 +2524,30 @@
         <v>18</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="7" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E57" s="7">
         <v>1</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>18</v>
@@ -2568,99 +2556,126 @@
         <v>18</v>
       </c>
       <c r="I57" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="7">
+        <v>2</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J57" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E58" s="14">
-        <v>13</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
+      <c r="J59" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>12</v>
+      <c r="A60" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="10">
+        <v>1</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="7" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E61" s="7">
         <v>1</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>18</v>
@@ -2669,30 +2684,30 @@
         <v>18</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="10" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E62" s="10">
         <v>1</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>18</v>
@@ -2701,30 +2716,30 @@
         <v>18</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="7" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E63" s="7">
         <v>1</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>18</v>
@@ -2733,30 +2748,30 @@
         <v>18</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>16</v>
-      </c>
       <c r="E64" s="10">
         <v>1</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G64" s="12" t="s">
         <v>18</v>
@@ -2765,30 +2780,30 @@
         <v>18</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="7" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="E65" s="7">
         <v>1</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>18</v>
@@ -2797,30 +2812,30 @@
         <v>18</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="10" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E66" s="10">
         <v>1</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>18</v>
@@ -2829,30 +2844,30 @@
         <v>18</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="7" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E67" s="7">
         <v>1</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>18</v>
@@ -2861,30 +2876,30 @@
         <v>18</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="10" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E68" s="10">
         <v>1</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>18</v>
@@ -2893,62 +2908,62 @@
         <v>18</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="7" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D69" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E69" s="7">
+        <v>1</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E69" s="7">
-        <v>1</v>
-      </c>
-      <c r="F69" s="9" t="s">
+      <c r="G69" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="G69" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>114</v>
-      </c>
       <c r="J69" s="9" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="10" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="E70" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="G70" s="12" t="s">
         <v>18</v>
@@ -2957,163 +2972,163 @@
         <v>18</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E71" s="7">
-        <v>1</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J71" s="9" t="s">
+      <c r="A71" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E71" s="14">
+        <v>18</v>
+      </c>
+      <c r="F71" s="13" t="s">
         <v>119</v>
       </c>
+      <c r="G71" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D72" s="11" t="s">
+      <c r="A72" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="7">
+        <v>1</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E72" s="10">
-        <v>1</v>
-      </c>
-      <c r="F72" s="12" t="s">
+      <c r="G74" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H72" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E73" s="14">
-        <v>12</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H73" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I73" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J73" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="3" t="s">
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>12</v>
+      <c r="C75" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="10">
+        <v>1</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="7" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="B76" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C76" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C76" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="D76" s="8" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="E76" s="7">
         <v>1</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="G76" s="9" t="s">
         <v>18</v>
@@ -3122,30 +3137,30 @@
         <v>18</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="10" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B77" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>127</v>
-      </c>
       <c r="D77" s="11" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="E77" s="10">
         <v>1</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>18</v>
@@ -3154,30 +3169,30 @@
         <v>18</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="7" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B78" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C78" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="D78" s="8" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="E78" s="7">
         <v>1</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G78" s="9" t="s">
         <v>18</v>
@@ -3186,30 +3201,30 @@
         <v>18</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="10" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E79" s="10">
         <v>1</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G79" s="12" t="s">
         <v>18</v>
@@ -3218,30 +3233,30 @@
         <v>18</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="7" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B80" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C80" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="D80" s="8" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E80" s="7">
         <v>1</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G80" s="9" t="s">
         <v>18</v>
@@ -3250,30 +3265,30 @@
         <v>18</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="10" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="E81" s="10">
         <v>1</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>18</v>
@@ -3282,30 +3297,30 @@
         <v>18</v>
       </c>
       <c r="I81" s="12" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="7" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E82" s="7">
         <v>1</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="G82" s="9" t="s">
         <v>18</v>
@@ -3314,38 +3329,38 @@
         <v>18</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E83" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F83" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J83" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="G83" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I83" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="J83" s="13" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3391,22 +3406,22 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="7" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="E86" s="7">
         <v>1</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="G86" s="9" t="s">
         <v>18</v>
@@ -3415,30 +3430,30 @@
         <v>18</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="10" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="E87" s="10">
         <v>1</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>18</v>
@@ -3447,15 +3462,15 @@
         <v>18</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="7" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>135</v>
@@ -3464,13 +3479,13 @@
         <v>136</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E88" s="7">
         <v>1</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G88" s="9" t="s">
         <v>18</v>
@@ -3479,30 +3494,30 @@
         <v>18</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="10" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E89" s="10">
         <v>1</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>18</v>
@@ -3511,30 +3526,30 @@
         <v>18</v>
       </c>
       <c r="I89" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="7" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="E90" s="7">
         <v>1</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>18</v>
@@ -3543,154 +3558,120 @@
         <v>18</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="10" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E92" s="14">
+        <v>6</v>
+      </c>
+      <c r="F92" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="G92" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E91" s="10">
-        <v>1</v>
-      </c>
-      <c r="F91" s="12" t="s">
+      <c r="J92" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="G91" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H91" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I91" s="12" t="s">
+    </row>
+    <row r="94" spans="1:10">
+      <c r="E94" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="J91" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E92" s="7">
-        <v>1</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J92" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E93" s="14">
-        <v>7</v>
-      </c>
-      <c r="F93" s="13" t="s">
+      <c r="F94" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="G93" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H93" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I93" s="13" t="s">
+      <c r="G94" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J94" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="E95" s="15">
+        <v>80</v>
+      </c>
+      <c r="F95" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="J93" s="13" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="E95" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="G95" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="H95" s="13" t="s">
+      <c r="G95" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="J95" s="16" t="s">
         <v>149</v>
-      </c>
-      <c r="I95" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="J95" s="13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="E96" s="15">
-        <v>70</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H96" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I96" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="J96" s="16" t="s">
-        <v>153</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:J72"/>
     <mergeCell ref="A83:D83"/>
     <mergeCell ref="A84:J84"/>
-    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A92:D92"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
